--- a/data/trans_bre/IP19C07-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 22,51</t>
+          <t>-12,15; 22,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 15,29</t>
+          <t>-16,92; 15,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 17,95</t>
+          <t>-9,71; 19,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 17,57</t>
+          <t>-3,66; 16,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,19; 461,75</t>
+          <t>-73,04; 514,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-81,51; 329,01</t>
+          <t>-88,32; 298,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-68,51; 377,01</t>
+          <t>-63,12; 505,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-59,31; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 5,88</t>
+          <t>-6,01; 6,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 4,58</t>
+          <t>-9,96; 4,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 15,9</t>
+          <t>1,39; 16,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 12,15</t>
+          <t>-7,32; 12,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-94,28; 359,41</t>
+          <t>-88,97; 573,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,07; 162,93</t>
+          <t>-87,18; 168,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,14 +795,14 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,07; 260,39</t>
+          <t>-55,38; 267,62</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 21,77</t>
+          <t>-10,11; 19,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 17,98</t>
+          <t>-9,86; 17,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,71</t>
+          <t>0,0; 15,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 16,45</t>
+          <t>-0,76; 15,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,71; 182,17</t>
+          <t>-42,97; 151,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,14; 196,75</t>
+          <t>-49,54; 201,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 9,7</t>
+          <t>-15,88; 10,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 10,14</t>
+          <t>-7,77; 10,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,17 +975,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 23,43</t>
+          <t>1,8; 20,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,17; 95,56</t>
+          <t>-63,62; 101,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-89,41; 591,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 10,52</t>
+          <t>-5,99; 10,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 2,83</t>
+          <t>-20,71; 0,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-36,88; 9,86</t>
+          <t>-34,52; 9,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 11,69</t>
+          <t>-5,19; 11,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 96,67</t>
+          <t>-96,05; 132,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,69; 11,78</t>
+          <t>-16,95; 12,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 16,88</t>
+          <t>-9,64; 16,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 19,36</t>
+          <t>-1,88; 19,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,98</t>
+          <t>0,0; 10,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-82,35; 141,57</t>
+          <t>-75,68; 167,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,44; 316,45</t>
+          <t>-54,77; 440,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,76; —</t>
+          <t>-65,79; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 13,78</t>
+          <t>-3,44; 13,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 11,61</t>
+          <t>-8,59; 11,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 14,93</t>
+          <t>-0,9; 14,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 9,46</t>
+          <t>-5,32; 10,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-38,84; 306,22</t>
+          <t>-34,62; 278,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-50,05; 124,57</t>
+          <t>-47,93; 130,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-40,88; 996,16</t>
+          <t>-30,72; 1340,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-60,01; 195,96</t>
+          <t>-52,46; 210,22</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 11,16</t>
+          <t>-2,98; 11,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 4,71</t>
+          <t>-6,96; 4,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 3,79</t>
+          <t>-10,15; 4,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 2,75</t>
+          <t>-10,33; 2,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,39; 308,13</t>
+          <t>-41,46; 329,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-80,16; 231,24</t>
+          <t>-83,76; 238,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-73,26; 65,35</t>
+          <t>-72,64; 64,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-88,43; 74,15</t>
+          <t>-87,9; 104,33</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 5,99</t>
+          <t>-1,62; 5,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,38</t>
+          <t>-3,7; 3,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 5,7</t>
+          <t>-0,67; 5,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 5,24</t>
+          <t>-0,94; 5,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 74,04</t>
+          <t>-13,8; 71,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-31,73; 41,55</t>
+          <t>-31,59; 47,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 130,64</t>
+          <t>-10,35; 134,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 119,51</t>
+          <t>-14,57; 119,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C07-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 22,06</t>
+          <t>-9,93; 22,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,92; 15,29</t>
+          <t>-16,38; 14,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 19,08</t>
+          <t>-10,56; 18,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 16,14</t>
+          <t>-3,49; 16,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,04; 514,66</t>
+          <t>-79,1; 463,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-88,32; 298,03</t>
+          <t>-79,8; 267,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-63,12; 505,6</t>
+          <t>-68,06; 471,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-59,31; —</t>
+          <t>-65,83; —</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 6,79</t>
+          <t>-5,77; 6,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 4,67</t>
+          <t>-10,03; 5,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 16,71</t>
+          <t>1,39; 17,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 12,25</t>
+          <t>-6,79; 12,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,97; 573,42</t>
+          <t>-100,0; 431,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,18; 168,86</t>
+          <t>-86,03; 179,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,38; 267,62</t>
+          <t>-52,32; 282,65</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 19,92</t>
+          <t>-10,01; 20,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 17,72</t>
+          <t>-10,81; 19,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,12</t>
+          <t>0,0; 12,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 15,2</t>
+          <t>-0,55; 15,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,97; 151,83</t>
+          <t>-42,12; 199,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 201,65</t>
+          <t>-50,78; 248,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 10,94</t>
+          <t>-17,86; 9,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 10,92</t>
+          <t>-8,28; 11,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,12 +975,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 20,88</t>
+          <t>1,45; 19,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,62; 101,84</t>
+          <t>-67,49; 84,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 10,96</t>
+          <t>-8,73; 10,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 0,57</t>
+          <t>-21,08; 0,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 9,77</t>
+          <t>-34,12; 10,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 11,03</t>
+          <t>-4,99; 12,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-96,05; 132,52</t>
+          <t>-100,0; 124,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 12,54</t>
+          <t>-16,62; 13,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 16,59</t>
+          <t>-8,84; 17,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 19,36</t>
+          <t>-0,08; 19,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,32</t>
+          <t>0,0; 8,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,68; 167,6</t>
+          <t>-75,7; 188,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,77; 440,16</t>
+          <t>-50,42; 394,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-65,79; —</t>
+          <t>-66,56; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 13,45</t>
+          <t>-3,56; 14,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 11,79</t>
+          <t>-8,23; 12,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 14,82</t>
+          <t>-0,92; 14,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 10,07</t>
+          <t>-5,31; 10,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 278,39</t>
+          <t>-32,31; 352,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-47,93; 130,26</t>
+          <t>-49,03; 140,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,72; 1340,58</t>
+          <t>-33,63; 1084,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-52,46; 210,22</t>
+          <t>-52,7; 240,15</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 11,43</t>
+          <t>-2,36; 11,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 4,51</t>
+          <t>-6,19; 4,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 4,37</t>
+          <t>-10,86; 3,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 2,46</t>
+          <t>-10,57; 1,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,46; 329,73</t>
+          <t>-32,22; 366,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-83,76; 238,51</t>
+          <t>-79,3; 271,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-72,64; 64,12</t>
+          <t>-71,58; 64,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-87,9; 104,33</t>
+          <t>-90,51; 67,95</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 5,96</t>
+          <t>-1,33; 5,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 3,63</t>
+          <t>-3,68; 3,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,6</t>
+          <t>-0,57; 5,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 5,13</t>
+          <t>-0,93; 5,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 71,75</t>
+          <t>-11,63; 67,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 47,55</t>
+          <t>-32,31; 43,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 134,34</t>
+          <t>-10,83; 126,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 119,18</t>
+          <t>-15,92; 117,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C07-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,4</t>
+          <t>5,98</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>102,2%</t>
+          <t>103,29%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 22,05</t>
+          <t>-11,68; 22,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 14,02</t>
+          <t>-14,96; 15,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 18,95</t>
+          <t>-11,21; 17,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 16,78</t>
+          <t>-3,49; 18,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-79,1; 463,3</t>
+          <t>-73,19; 461,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-79,8; 267,62</t>
+          <t>-81,51; 329,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-68,06; 471,37</t>
+          <t>-68,51; 377,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-65,83; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,54</t>
+          <t>3,61</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>39,11%</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 6,64</t>
+          <t>-5,91; 5,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 5,0</t>
+          <t>-10,2; 4,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 17,23</t>
+          <t>0,73; 15,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 12,28</t>
+          <t>-8,22; 13,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 431,55</t>
+          <t>-94,28; 359,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,03; 179,97</t>
+          <t>-87,07; 162,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,32; 282,65</t>
+          <t>-55,95; 299,94</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,88</t>
+          <t>4,91</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>355,77%</t>
+          <t>382,79%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 20,9</t>
+          <t>-10,79; 21,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 19,98</t>
+          <t>-10,81; 17,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,05</t>
+          <t>0,0; 12,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 15,29</t>
+          <t>-0,94; 16,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,12; 199,59</t>
+          <t>-42,71; 182,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,78; 248,65</t>
+          <t>-50,14; 196,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,3</t>
+          <t>9,08</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>918,74%</t>
+          <t>1086,27%</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 9,76</t>
+          <t>-17,02; 9,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 11,3</t>
+          <t>-7,95; 10,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,17 +975,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 19,23</t>
+          <t>2,14; 24,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,49; 84,74</t>
+          <t>-66,17; 95,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,41; 591,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 10,65</t>
+          <t>-6,78; 10,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 0,3</t>
+          <t>-20,21; 2,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-34,12; 10,21</t>
+          <t>-36,88; 9,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 12,6</t>
+          <t>-5,14; 11,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 124,01</t>
+          <t>-100,0; 96,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>1,82</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 13,84</t>
+          <t>-18,69; 11,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 17,92</t>
+          <t>-10,38; 16,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 19,54</t>
+          <t>-1,65; 19,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,34</t>
+          <t>0,0; 9,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,7; 188,07</t>
+          <t>-82,35; 141,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-50,42; 394,07</t>
+          <t>-56,44; 316,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-66,56; —</t>
+          <t>-59,76; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>1,36</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 14,3</t>
+          <t>-4,46; 13,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 12,24</t>
+          <t>-8,8; 11,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 14,36</t>
+          <t>-0,95; 14,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 10,95</t>
+          <t>-6,78; 9,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,31; 352,87</t>
+          <t>-38,84; 306,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-49,03; 140,47</t>
+          <t>-50,05; 124,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-33,63; 1084,58</t>
+          <t>-40,88; 996,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-52,7; 240,15</t>
+          <t>-60,31; 191,08</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-4,0</t>
+          <t>-4,37</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-50,36%</t>
+          <t>-54,27%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 11,42</t>
+          <t>-2,94; 11,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 4,91</t>
+          <t>-6,24; 4,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 3,76</t>
+          <t>-10,7; 3,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 1,92</t>
+          <t>-10,56; 1,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,22; 366,2</t>
+          <t>-43,39; 308,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,3; 271,41</t>
+          <t>-80,16; 231,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-71,58; 64,87</t>
+          <t>-73,26; 65,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-90,51; 67,95</t>
+          <t>-89,2; 79,73</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>1,89</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 5,87</t>
+          <t>-1,57; 5,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 3,59</t>
+          <t>-3,53; 3,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 5,75</t>
+          <t>-0,68; 5,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 5,24</t>
+          <t>-1,33; 5,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 67,62</t>
+          <t>-13,72; 74,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-32,31; 43,71</t>
+          <t>-31,73; 41,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 126,84</t>
+          <t>-12,12; 130,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 117,42</t>
+          <t>-19,25; 111,24</t>
         </is>
       </c>
     </row>
